--- a/docs/Working Paper/QMFM parameter comparison May2023-EvM rev Dec2025.xlsx
+++ b/docs/Working Paper/QMFM parameter comparison May2023-EvM rev Dec2025.xlsx
@@ -8,16 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\GitHub\QMFM\docs\Working Paper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB45876F-CD16-4563-A3AA-E598DC29A378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6B4F14-1848-4CFF-B001-5B9CB50391F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{88228A9F-2F45-4AC0-AF82-DDE885F9A54D}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" activeTab="1" xr2:uid="{88228A9F-2F45-4AC0-AF82-DDE885F9A54D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Param" sheetId="2" r:id="rId1"/>
+    <sheet name="WP" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$2:$J$237</definedName>
-    <definedName name="tab_param">Sheet1!$A$2:$J$237</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Param!$A$2:$J$237</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">WP!$B$1:$C$225</definedName>
+    <definedName name="tab_param" localSheetId="0">Param!$A$2:$J$237</definedName>
+    <definedName name="tab_param">WP!$B$1:$C$225</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +37,7 @@
     <author>ak</author>
   </authors>
   <commentList>
-    <comment ref="F38" authorId="0" shapeId="0" xr:uid="{69B61766-AB1C-404E-93EB-B230C6A6FEA0}">
+    <comment ref="F38" authorId="0" shapeId="0" xr:uid="{03AC9E1A-2423-4706-80AF-755330236EA1}">
       <text>
         <r>
           <rPr>
@@ -58,7 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E42" authorId="0" shapeId="0" xr:uid="{DE81B7D7-7800-4A06-97B1-C147B0C7334B}">
+    <comment ref="E42" authorId="0" shapeId="0" xr:uid="{CD38146F-A0B3-4CEA-99C9-624AD8F19A5E}">
       <text>
         <r>
           <rPr>
@@ -82,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F42" authorId="0" shapeId="0" xr:uid="{760F9005-D0AE-41A6-8C26-B289FB35CE1D}">
+    <comment ref="F42" authorId="0" shapeId="0" xr:uid="{FC5DDC3E-DBEA-4701-8E0C-7210EF771714}">
       <text>
         <r>
           <rPr>
@@ -106,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{5FC5EB0C-7995-4C6B-A472-DA57A1AA0CC2}">
+    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{847D569C-DEE1-4529-96C6-B07C6158DDB8}">
       <text>
         <r>
           <rPr>
@@ -130,7 +133,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F47" authorId="0" shapeId="0" xr:uid="{165A84CC-2A1A-4AE5-9AE9-7DE201E462D8}">
+    <comment ref="F47" authorId="0" shapeId="0" xr:uid="{498CC6CE-F16E-4BE0-B0FE-C9C24ABDF5F6}">
       <text>
         <r>
           <rPr>
@@ -154,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{0969415C-12F1-4ABB-8037-C47503D184CE}">
+    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{646D358D-7642-44EF-9D9C-B97DDAA50F30}">
       <text>
         <r>
           <rPr>
@@ -178,7 +181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F60" authorId="0" shapeId="0" xr:uid="{36D57198-C040-48DC-A060-50F2A58DE489}">
+    <comment ref="F60" authorId="0" shapeId="0" xr:uid="{A354A2EB-A550-47FB-96F6-EF1187C484DB}">
       <text>
         <r>
           <rPr>
@@ -202,7 +205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F62" authorId="0" shapeId="0" xr:uid="{4C3C73E3-33BD-4CC5-9ABA-FAEC76731081}">
+    <comment ref="F62" authorId="0" shapeId="0" xr:uid="{B479F79C-5D51-4C8B-9F9D-FBBE595B1048}">
       <text>
         <r>
           <rPr>
@@ -226,7 +229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E65" authorId="0" shapeId="0" xr:uid="{5A46C81E-58F5-473F-B664-62B6479516D0}">
+    <comment ref="E65" authorId="0" shapeId="0" xr:uid="{C4EF90EE-094C-492B-9710-710E65F3D77B}">
       <text>
         <r>
           <rPr>
@@ -250,7 +253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{1024EB0B-344C-4C4D-A3DD-ABC72A5BDDBF}">
+    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{BBCCA4F2-D5E7-4E43-AE73-B5FD5BF47222}">
       <text>
         <r>
           <rPr>
@@ -274,7 +277,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F66" authorId="0" shapeId="0" xr:uid="{1D0E8769-F39D-4690-8F70-60015C282B1B}">
+    <comment ref="F66" authorId="0" shapeId="0" xr:uid="{2D10109D-D7FE-401D-923E-C7D82BD8E5CF}">
       <text>
         <r>
           <rPr>
@@ -287,7 +290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C72" authorId="0" shapeId="0" xr:uid="{B4A762E4-7F23-41FD-B907-2959F517264E}">
+    <comment ref="C72" authorId="0" shapeId="0" xr:uid="{AB447785-5DFE-4A5E-A912-39B2E187C154}">
       <text>
         <r>
           <rPr>
@@ -295,7 +298,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>ak:</t>
         </r>
@@ -304,14 +307,14 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 non-agric output gap</t>
         </r>
       </text>
     </comment>
-    <comment ref="D74" authorId="0" shapeId="0" xr:uid="{B5B4011F-A9D5-4D00-A634-87FAD653DCCF}">
+    <comment ref="D74" authorId="0" shapeId="0" xr:uid="{40ECDA38-9B16-459B-B1A3-1BC865895ADF}">
       <text>
         <r>
           <rPr>
@@ -335,7 +338,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H76" authorId="0" shapeId="0" xr:uid="{A037DC90-611F-4A31-ADEE-DF5A7BA17213}">
+    <comment ref="H76" authorId="0" shapeId="0" xr:uid="{1265D019-7523-49AB-B4FD-2A0F6C8EE980}">
       <text>
         <r>
           <rPr>
@@ -343,7 +346,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>ak:</t>
         </r>
@@ -352,14 +355,14 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 one quarter lag</t>
         </r>
       </text>
     </comment>
-    <comment ref="F81" authorId="0" shapeId="0" xr:uid="{733857EB-C9FB-499B-937A-8C6B4EB04DE8}">
+    <comment ref="F81" authorId="0" shapeId="0" xr:uid="{4870B8FD-D089-4BF4-A578-94341AE133D9}">
       <text>
         <r>
           <rPr>
@@ -383,7 +386,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E82" authorId="0" shapeId="0" xr:uid="{3A6A933C-9C8E-463A-B7B7-A677601EA3A0}">
+    <comment ref="E82" authorId="0" shapeId="0" xr:uid="{83B4D433-E5B8-42C8-88E7-893F1C85BCED}">
       <text>
         <r>
           <rPr>
@@ -407,7 +410,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F85" authorId="0" shapeId="0" xr:uid="{EE5D801E-8E17-440D-96E3-C5A2D23848AF}">
+    <comment ref="F85" authorId="0" shapeId="0" xr:uid="{BE481432-659F-4C4C-8631-723E09CDBAA8}">
       <text>
         <r>
           <rPr>
@@ -431,7 +434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G87" authorId="0" shapeId="0" xr:uid="{B7D5746E-6689-4381-873A-C5342727147E}">
+    <comment ref="G87" authorId="0" shapeId="0" xr:uid="{DCC7EA79-5568-4D02-BD9F-7E735432EB27}">
       <text>
         <r>
           <rPr>
@@ -455,7 +458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E91" authorId="0" shapeId="0" xr:uid="{8EDD43A9-446F-485B-B9D2-234080C6A55E}">
+    <comment ref="E91" authorId="0" shapeId="0" xr:uid="{4A7BB1FE-F1E0-4666-8C68-F9883C668CDB}">
       <text>
         <r>
           <rPr>
@@ -468,7 +471,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J91" authorId="0" shapeId="0" xr:uid="{A8B42748-A6A4-45E8-9304-E5E01329E2E0}">
+    <comment ref="J91" authorId="0" shapeId="0" xr:uid="{E37B02B8-D671-411C-98E6-12D59E4A5A0D}">
       <text>
         <r>
           <rPr>
@@ -492,7 +495,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C102" authorId="0" shapeId="0" xr:uid="{FCB2F797-ECFA-456B-9AFC-5E90F2463BCF}">
+    <comment ref="C102" authorId="0" shapeId="0" xr:uid="{A029549D-24F5-4A25-9ABE-F1418C99A7A5}">
       <text>
         <r>
           <rPr>
@@ -517,7 +520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G104" authorId="0" shapeId="0" xr:uid="{0725577C-F136-4F87-9C27-2A831CF8FA6B}">
+    <comment ref="G104" authorId="0" shapeId="0" xr:uid="{E5CF89B7-240D-4357-9B69-773D1BF06406}">
       <text>
         <r>
           <rPr>
@@ -541,7 +544,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C113" authorId="0" shapeId="0" xr:uid="{F2F5B4E9-B309-404A-92D0-F8A769B24892}">
+    <comment ref="C113" authorId="0" shapeId="0" xr:uid="{80324C0E-936C-4F10-95E9-A0BE983A15FA}">
       <text>
         <r>
           <rPr>
@@ -565,7 +568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D113" authorId="0" shapeId="0" xr:uid="{BD5910D4-DE96-4459-94E0-EF74563C68A6}">
+    <comment ref="D113" authorId="0" shapeId="0" xr:uid="{485CF869-3384-45D7-9B1D-54F0B8F2131E}">
       <text>
         <r>
           <rPr>
@@ -589,7 +592,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C118" authorId="0" shapeId="0" xr:uid="{6BB70441-5753-4A5A-9635-92C6AE9BD86C}">
+    <comment ref="C118" authorId="0" shapeId="0" xr:uid="{C261C12F-4ECE-4AB4-93CD-3E28B65E3477}">
       <text>
         <r>
           <rPr>
@@ -602,7 +605,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D118" authorId="0" shapeId="0" xr:uid="{E355C3E0-01B0-4146-A9AF-8F6C37DB9CBC}">
+    <comment ref="D118" authorId="0" shapeId="0" xr:uid="{6110A840-70F8-4F96-8645-0A9FACD109D2}">
       <text>
         <r>
           <rPr>
@@ -615,7 +618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E118" authorId="0" shapeId="0" xr:uid="{131DF51D-E8D5-4981-8836-E529A92D9D8F}">
+    <comment ref="E118" authorId="0" shapeId="0" xr:uid="{2E112F9C-7EA2-48AD-95F2-2FFBD0FF0762}">
       <text>
         <r>
           <rPr>
@@ -628,7 +631,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{4A8E023F-ABB1-4917-B171-4A12742E7711}">
+    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{A171A6B4-08EF-423A-97D0-57D5A572753A}">
       <text>
         <r>
           <rPr>
@@ -641,7 +644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G118" authorId="0" shapeId="0" xr:uid="{41AB4C7C-7DA4-4636-AFDC-5C83BAA5B316}">
+    <comment ref="G118" authorId="0" shapeId="0" xr:uid="{C3D3C402-7919-4C21-8C33-BDC6AA895A61}">
       <text>
         <r>
           <rPr>
@@ -654,7 +657,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H118" authorId="0" shapeId="0" xr:uid="{5159631A-B37C-47FC-ADC1-09102C938E27}">
+    <comment ref="H118" authorId="0" shapeId="0" xr:uid="{384FE71D-32B5-4BED-8336-58244EF38352}">
       <text>
         <r>
           <rPr>
@@ -667,7 +670,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C119" authorId="0" shapeId="0" xr:uid="{F013E585-2668-4540-B06F-40495D1BD818}">
+    <comment ref="C119" authorId="0" shapeId="0" xr:uid="{2DF7DC62-8BE8-42F8-8114-D8EF95980AB3}">
       <text>
         <r>
           <rPr>
@@ -681,7 +684,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D119" authorId="0" shapeId="0" xr:uid="{26CDC5AF-47A1-41E2-B40D-11B6C64D63F7}">
+    <comment ref="D119" authorId="0" shapeId="0" xr:uid="{CFA8B524-850C-4889-AA6F-DA7C41E0CDD1}">
       <text>
         <r>
           <rPr>
@@ -695,7 +698,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C122" authorId="0" shapeId="0" xr:uid="{20436728-96F7-49E8-AA95-E3028DE642BE}">
+    <comment ref="C122" authorId="0" shapeId="0" xr:uid="{80725690-62AE-42C5-A611-BD9D7101C6D1}">
       <text>
         <r>
           <rPr>
@@ -719,7 +722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B135" authorId="0" shapeId="0" xr:uid="{960042AA-5DDF-4AA3-9BFD-05D4FC4FE253}">
+    <comment ref="B135" authorId="0" shapeId="0" xr:uid="{D7E0C1C8-CF46-4E01-BA2A-2681214CAC76}">
       <text>
         <r>
           <rPr>
@@ -763,7 +766,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C135" authorId="0" shapeId="0" xr:uid="{773596E3-EB7E-4948-8C35-25904B434150}">
+    <comment ref="C135" authorId="0" shapeId="0" xr:uid="{BF41DF19-5148-468B-B663-3590A2564BF7}">
       <text>
         <r>
           <rPr>
@@ -807,7 +810,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D160" authorId="0" shapeId="0" xr:uid="{72324EB6-8186-41BB-9C87-E9694851086D}">
+    <comment ref="D160" authorId="0" shapeId="0" xr:uid="{C4AB68FA-AF78-4DA2-9261-4D1DD557FB44}">
       <text>
         <r>
           <rPr>
@@ -831,7 +834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H160" authorId="0" shapeId="0" xr:uid="{953BF745-32F4-4573-A361-64DDA4B2BC96}">
+    <comment ref="H160" authorId="0" shapeId="0" xr:uid="{C3A97D62-865F-4E66-ADA5-678195F9641C}">
       <text>
         <r>
           <rPr>
@@ -856,7 +859,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C161" authorId="0" shapeId="0" xr:uid="{D7BD2CA0-D9D7-4050-A2C4-3D71E024848C}">
+    <comment ref="C161" authorId="0" shapeId="0" xr:uid="{4F000BF5-7CEA-45E0-915B-F14799A4E853}">
       <text>
         <r>
           <rPr>
@@ -880,7 +883,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D161" authorId="0" shapeId="0" xr:uid="{19350209-6B8C-4E6F-9BBE-C7BB3DFCD08C}">
+    <comment ref="D161" authorId="0" shapeId="0" xr:uid="{DBB2CB1A-E860-4D47-920B-A4DE3770295C}">
       <text>
         <r>
           <rPr>
@@ -904,7 +907,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F161" authorId="0" shapeId="0" xr:uid="{075CD574-269B-4E9C-B28C-00FAC94F6775}">
+    <comment ref="F161" authorId="0" shapeId="0" xr:uid="{1F0CB7CD-47E4-4008-B054-F412A1236699}">
       <text>
         <r>
           <rPr>
@@ -929,7 +932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G161" authorId="0" shapeId="0" xr:uid="{6702AC96-06F3-4480-812D-94D09217A4F7}">
+    <comment ref="G161" authorId="0" shapeId="0" xr:uid="{6704C0F1-6198-4890-AFC2-4EC372073B55}">
       <text>
         <r>
           <rPr>
@@ -953,7 +956,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H161" authorId="0" shapeId="0" xr:uid="{7ADB7146-AAE8-4DC5-80B9-3711DD8804EE}">
+    <comment ref="H161" authorId="0" shapeId="0" xr:uid="{E2C769D0-726E-4541-9689-3A7ABCA77F54}">
       <text>
         <r>
           <rPr>
@@ -977,7 +980,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H177" authorId="0" shapeId="0" xr:uid="{F52A4805-1468-4454-856A-BFE867DA6461}">
+    <comment ref="H177" authorId="0" shapeId="0" xr:uid="{EE4C532E-0E07-4D21-9F59-DFA9C7E127EC}">
       <text>
         <r>
           <rPr>
@@ -1002,7 +1005,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B186" authorId="0" shapeId="0" xr:uid="{43672FF8-4E0D-4088-A876-A1DCAE9DED30}">
+    <comment ref="B186" authorId="0" shapeId="0" xr:uid="{68EA9D02-1CD7-48D4-BB25-A0C9EEBCD02B}">
       <text>
         <r>
           <rPr>
@@ -1018,14 +1021,14 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="H191" authorId="0" shapeId="0" xr:uid="{E8293776-81F3-4DD2-9844-86C595A79DE8}">
+    <comment ref="H191" authorId="0" shapeId="0" xr:uid="{E67EC4EF-0E0F-4BBE-BFC7-1EE73FEEEA59}">
       <text>
         <r>
           <rPr>
@@ -1050,7 +1053,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F205" authorId="0" shapeId="0" xr:uid="{07086359-F139-421C-A489-16E03A83A310}">
+    <comment ref="F205" authorId="0" shapeId="0" xr:uid="{AE46C132-7A1F-4F7B-994C-93679A29107C}">
       <text>
         <r>
           <rPr>
@@ -1075,7 +1078,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D208" authorId="0" shapeId="0" xr:uid="{B0FC95F5-620C-45B6-9580-EFEFC2285766}">
+    <comment ref="D208" authorId="0" shapeId="0" xr:uid="{A314C01D-4B18-4544-8877-509B6DFE1AD7}">
       <text>
         <r>
           <rPr>
@@ -1099,7 +1102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F208" authorId="0" shapeId="0" xr:uid="{E4697C52-4A12-4583-B41B-AE0AC2F56AE8}">
+    <comment ref="F208" authorId="0" shapeId="0" xr:uid="{F3831853-1074-41C5-95AF-AA7C81DFE400}">
       <text>
         <r>
           <rPr>
@@ -1123,7 +1126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G208" authorId="0" shapeId="0" xr:uid="{276B5677-607F-4E47-A5EA-773DF4821A01}">
+    <comment ref="G208" authorId="0" shapeId="0" xr:uid="{7183852C-6400-405A-ACA1-79D129BA5155}">
       <text>
         <r>
           <rPr>
@@ -1147,7 +1150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F209" authorId="0" shapeId="0" xr:uid="{1F1C180D-E032-4C5B-AEF9-7CF95D0F1775}">
+    <comment ref="F209" authorId="0" shapeId="0" xr:uid="{5E9CEF48-5468-4CDB-BC4E-032D96A283AC}">
       <text>
         <r>
           <rPr>
@@ -1176,8 +1179,85 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>ak</author>
+  </authors>
+  <commentList>
+    <comment ref="C123" authorId="0" shapeId="0" xr:uid="{960042AA-5DDF-4AA3-9BFD-05D4FC4FE253}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ak:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+multiplied by (1-m1)=0.3 overall </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 0.15
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C174" authorId="0" shapeId="0" xr:uid="{43672FF8-4E0D-4088-A876-A1DCAE9DED30}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ak: e^(-4) =0.02</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="451">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -2573,9 +2653,6 @@
   </si>
   <si>
     <t>d7 = 0.5</t>
-  </si>
-  <si>
-    <t>ss_oexp_y_str = 6, (1-u3) * (1-u3) * ss_oexp_y_str = 0.3</t>
   </si>
   <si>
     <t>u3 = 0</t>
@@ -3334,6 +3411,478 @@
       </rPr>
       <t xml:space="preserve"> (0.8) </t>
     </r>
+  </si>
+  <si>
+    <t>ss_oexp_y_str = 6, (1-u3) * ss_oexp_y_str = 0.3</t>
+  </si>
+  <si>
+    <t>a4_cons   = 0.2 (0.3)</t>
+  </si>
+  <si>
+    <t>Weight of RIR in RMCI (or RIR direct effect, if RMCI n.a.)</t>
+  </si>
+  <si>
+    <t>a4_inv   = 0.2 (0.3)</t>
+  </si>
+  <si>
+    <t>a3_exp  = 0.2 (0.1)</t>
+  </si>
+  <si>
+    <t>a5_exp  = 0.3 (0.5)</t>
+  </si>
+  <si>
+    <t>w_imp_cons  = 0.4457 (0.23 (0.30/1.30))</t>
+  </si>
+  <si>
+    <t>w_imp_inv   = 0.156 (0.31 (0.40/1.30))</t>
+  </si>
+  <si>
+    <t>w_imp_gdem  =  0.2760 (0.31 (0.40/1.30))</t>
+  </si>
+  <si>
+    <t>w_imp_exp   = 0.1223 (0.15 (0.20/1.30))</t>
+  </si>
+  <si>
+    <t>w_y_inv     = 0.13(0.3)</t>
+  </si>
+  <si>
+    <t>bf1 = 0.35 (0.5, faster adjustment)</t>
+  </si>
+  <si>
+    <t>be1 = 0.25 (0.5, faster adjustment)</t>
+  </si>
+  <si>
+    <t>c1 = 0.8 (0.5)</t>
+  </si>
+  <si>
+    <t>e1 = 0.50 (0.2)</t>
+  </si>
+  <si>
+    <t>e2 = 0.50, e1*e2 = 0.25 (0.2)</t>
+  </si>
+  <si>
+    <t>ss_debt_fcy_rat  =  0.85 (55/65)</t>
+  </si>
+  <si>
+    <t>ss_dl_y_tnd =  100*log(1 + 7.5/100) = 7.2321</t>
+  </si>
+  <si>
+    <t>ss_dl_y_agr_tnd = 100*log(1 + 8/100) = 7.2321</t>
+  </si>
+  <si>
+    <t>ss_d4l_cpi_tar = 100*log(1 + 5/100) = 4.879</t>
+  </si>
+  <si>
+    <t>ss_prem_debt_fcy  = NaN (0.5)</t>
+  </si>
+  <si>
+    <t>ss_prem_debt_lcy  = NaN (2.8)</t>
+  </si>
+  <si>
+    <t>ss_istar = 2 (in model: = ss of r* + CPI*)</t>
+  </si>
+  <si>
+    <t>std_shock_l_ystar_gap         = 0.45 (0.25)</t>
+  </si>
+  <si>
+    <r>
+      <t>Weights of demand components in Output gap (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>∑=1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phillips curve core inflation (π</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>core</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>)--dl_cpi_core</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phillips curve food inflation (π</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>food</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>)--dl_cpi_food</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Agricultural output gap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (l_y_agr_gap, negative in equation)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phillips curve energy inflation (π</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>energy</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>)--dl_cpi_ener</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Exchange rate depreciation </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>rate, deviation from target</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Consumption (=</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> output trend</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> persistence etc. )</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Relative price food </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>(relative to headline CPI)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Relative price energy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>(relative to headline CPI)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Trend growth relative price food</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (relative to headline)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trend growth relative price energy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>(relative to headline)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Domestic lending premium </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>(over policy rate)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Government foreign borrowing premium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (discount)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Government dom. borrowing premium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (over policy rate)</t>
+    </r>
+  </si>
+  <si>
+    <t>ss_dl_v  =  100*log(1 - 2/100)  ≈ -2.0203</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trend dom.real interest rate </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>(foreign RIR+premium+RERdepr_tnd)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Standard deviation </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>(σ or SE=σ/√n)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Foreign output gap </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Rwanda trading partners)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Foreign CPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Rwanda trading partners)</t>
+    </r>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>RIR trend persistence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma_k = 0.50 (0.8) </t>
+  </si>
+  <si>
+    <r>
+      <t>b1  = 0.35 (0.45 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Bahnschrift Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.35)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>b3  = 0.05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Bahnschrift Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (&lt;&lt; import share =0.20 partial pass-thru, stability!)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>bf3 = 0.10 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Bahnschrift Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.03)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">be3 = 0.20 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Bahnschrift Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>(0.03,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ss_dl_rp_cpi_food_tnd = 100*log(1 + 2/100) = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Bahnschrift Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>1.9803</t>
+    </r>
+  </si>
+  <si>
+    <t>1 - b4 = 0.2</t>
+  </si>
+  <si>
+    <t>c2  = 1.20, (1 - c1) * c2 = 0.16 (0.50, (1 - c1)*c2 = 0.10)</t>
+  </si>
+  <si>
+    <t>Automatic stabilizer effect, weight of outgap</t>
+  </si>
+  <si>
+    <t>u1 = 0</t>
+  </si>
+  <si>
+    <t>u2 = 0.012</t>
+  </si>
+  <si>
+    <t>I. Fiscal/budget sector</t>
+  </si>
+  <si>
+    <t>1. Fiscal deficit (def_y = gdem_y + oexp_y - grev_y)</t>
+  </si>
+  <si>
+    <t>1.2. Structural component (def_y_str)</t>
+  </si>
+  <si>
+    <t>1.1. Cyclical component (def_y_cyc)</t>
+  </si>
+  <si>
+    <t>Weight discretionary deficit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steady state </t>
+  </si>
+  <si>
+    <t>Weight of RER in RMCI (or RER direct effect if RMCI n.a)</t>
   </si>
 </sst>
 </file>
@@ -3343,7 +3892,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="49">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3519,19 +4068,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
@@ -3605,6 +4141,93 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Bahnschrift Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Bahnschrift Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Bahnschrift Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Bahnschrift Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Bahnschrift Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Bahnschrift Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Bahnschrift "/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -3626,7 +4249,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -3686,11 +4309,83 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="slantDashDot">
+        <color indexed="64"/>
+      </left>
+      <right style="slantDashDot">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="slantDashDot">
+        <color indexed="64"/>
+      </left>
+      <right style="slantDashDot">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="slantDashDot">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="slantDashDot">
+        <color indexed="64"/>
+      </left>
+      <right style="slantDashDot">
+        <color indexed="64"/>
+      </right>
+      <top style="slantDashDot">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="slantDashDot">
+        <color indexed="64"/>
+      </right>
+      <top style="slantDashDot">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="slantDashDot">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="slantDashDot">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="slantDashDot">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3795,34 +4490,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3847,7 +4542,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3865,6 +4560,36 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3900,6 +4625,74 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>2464954</xdr:colOff>
       <xdr:row>30</xdr:row>
+      <xdr:rowOff>150091</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Isosceles Triangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DA27E78-D334-497D-8267-226F79EE34F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2398568" y="5683250"/>
+          <a:ext cx="66386" cy="86591"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-RW" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2398568</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2464954</xdr:colOff>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>150091</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4251,9 +5044,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DA45FF5-F233-4AC2-840A-6D28A8836A24}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF104713-EB19-4CF2-B423-1946DFA71225}">
   <dimension ref="A1:L237"/>
-  <sheetFormatPr defaultRowHeight="14.75" outlineLevelRow="1" outlineLevelCol="2" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.75" outlineLevelRow="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="50.81640625" customWidth="1"/>
     <col min="2" max="2" width="32.36328125" style="2" customWidth="1"/>
@@ -4267,12 +5060,12 @@
     <col min="12" max="12" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:12">
       <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
@@ -4281,7 +5074,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="10"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:12">
       <c r="B3" s="7"/>
       <c r="C3" s="10"/>
       <c r="D3" s="4"/>
@@ -4293,7 +5086,7 @@
       <c r="J3" s="4"/>
       <c r="K3" s="29"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:12">
       <c r="A4" s="8" t="s">
         <v>310</v>
       </c>
@@ -4329,7 +5122,7 @@
       </c>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:12" s="7" customFormat="1">
       <c r="C5" s="18" t="s">
         <v>2</v>
       </c>
@@ -4359,7 +5152,7 @@
       </c>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:12">
       <c r="A6" s="56" t="s">
         <v>307</v>
       </c>
@@ -4368,27 +5161,30 @@
         <v>n.a.</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="K7" s="13"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
         <v>311</v>
       </c>
       <c r="K8" s="13"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
         <v>308</v>
       </c>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>302</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>443</v>
       </c>
       <c r="C10" s="13">
         <v>0.4</v>
@@ -4401,26 +5197,26 @@
         <v>n.a.</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>303</v>
       </c>
       <c r="B11" s="55" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>241</v>
       </c>
       <c r="G11" s="9"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:12">
       <c r="A12" s="1" t="s">
         <v>309</v>
       </c>
       <c r="C12" s="13"/>
       <c r="G12" s="9"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:12">
       <c r="A13" s="42" t="s">
         <v>312</v>
       </c>
@@ -4430,7 +5226,7 @@
       <c r="C13" s="13"/>
       <c r="G13" s="9"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:12">
       <c r="A14" s="42" t="s">
         <v>313</v>
       </c>
@@ -4440,7 +5236,7 @@
       <c r="C14" s="13"/>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:12">
       <c r="A15" s="42" t="s">
         <v>314</v>
       </c>
@@ -4450,12 +5246,12 @@
       <c r="C15" s="13"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:12">
       <c r="A16" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:7">
       <c r="A17" s="42" t="s">
         <v>303</v>
       </c>
@@ -4463,7 +5259,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:7">
       <c r="A18" s="42" t="s">
         <v>318</v>
       </c>
@@ -4471,13 +5267,13 @@
         <v>317</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:7">
       <c r="A19" s="42"/>
       <c r="B19" s="55"/>
       <c r="C19" s="13"/>
       <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
         <v>324</v>
       </c>
@@ -4485,7 +5281,7 @@
       <c r="C20" s="13"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
         <v>319</v>
       </c>
@@ -4493,7 +5289,7 @@
       <c r="C21" s="13"/>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>303</v>
       </c>
@@ -4505,19 +5301,19 @@
       </c>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>321</v>
       </c>
       <c r="B23" s="55" t="s">
-        <v>331</v>
+        <v>388</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>241</v>
       </c>
       <c r="G23" s="9"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
         <v>309</v>
       </c>
@@ -4525,7 +5321,7 @@
       <c r="C24" s="13"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:7">
       <c r="A25" s="42" t="s">
         <v>303</v>
       </c>
@@ -4533,20 +5329,20 @@
         <v>322</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>321</v>
       </c>
       <c r="B26" s="55" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.75">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.75">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>303</v>
       </c>
@@ -4554,22 +5350,22 @@
         <v>323</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>321</v>
       </c>
       <c r="B29" s="55" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.75">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
         <v>329</v>
       </c>
       <c r="C31" s="13"/>
       <c r="G31" s="9"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>327</v>
       </c>
@@ -4581,14 +5377,14 @@
       </c>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:11">
       <c r="A33" s="1" t="s">
         <v>328</v>
       </c>
       <c r="C33" s="13"/>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
         <v>303</v>
       </c>
@@ -4600,29 +5396,29 @@
       </c>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:11">
       <c r="A35" s="42" t="s">
         <v>325</v>
       </c>
       <c r="B35" s="54" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G35" s="9"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:11">
       <c r="A36" s="42"/>
       <c r="B36" s="54"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:11">
       <c r="A37" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G37" s="9"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:11">
       <c r="A38" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C38" s="13" t="str">
         <f>+D38</f>
@@ -4640,7 +5436,7 @@
         <v>n.a.</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -4655,7 +5451,7 @@
       </c>
       <c r="G39" s="9"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
         <v>10</v>
       </c>
@@ -4672,7 +5468,7 @@
       </c>
       <c r="G40" s="9"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
         <v>29</v>
       </c>
@@ -4687,12 +5483,12 @@
       </c>
       <c r="G41" s="9"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:11">
       <c r="A42" t="s">
         <v>11</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E42" s="31">
         <v>7.1999999999999995E-2</v>
@@ -4702,12 +5498,12 @@
       </c>
       <c r="G42" s="9"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
         <v>12</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E43" s="32" t="s">
         <v>250</v>
@@ -4717,7 +5513,7 @@
       </c>
       <c r="G43" s="9"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
         <v>278</v>
       </c>
@@ -4732,7 +5528,7 @@
       </c>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:11">
       <c r="A45" s="3" t="s">
         <v>279</v>
       </c>
@@ -4745,15 +5541,15 @@
       </c>
       <c r="G45" s="9"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:11">
       <c r="A46" s="3"/>
       <c r="E46" s="40"/>
       <c r="F46" s="42"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:11">
       <c r="A47" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C47" s="13" t="str">
         <f>+D47</f>
@@ -4771,7 +5567,7 @@
         <v>n.a.</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:11">
       <c r="A48" t="str">
         <f t="shared" ref="A48:A53" si="0">+A39</f>
         <v>Lag, persistence (AR1)</v>
@@ -4784,7 +5580,7 @@
       </c>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:11">
       <c r="A49" t="str">
         <f t="shared" si="0"/>
         <v>Expectation (t+1)</v>
@@ -4798,7 +5594,7 @@
       </c>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:11">
       <c r="A50" t="str">
         <f t="shared" si="0"/>
         <v>Real Monetary Conditions Index (RMCI)</v>
@@ -4811,33 +5607,33 @@
       </c>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:11">
       <c r="A51" t="str">
         <f t="shared" si="0"/>
         <v>Output gap</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E51">
         <v>0.1</v>
       </c>
       <c r="G51" s="9"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:11">
       <c r="A52" t="str">
         <f t="shared" si="0"/>
         <v>Fiscal impulse</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E52" s="13" t="s">
         <v>250</v>
       </c>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:11">
       <c r="A53" t="str">
         <f t="shared" si="0"/>
         <v>Weight of RIR in RMCI (or RIR direct effect, if RMCI n.a.)</v>
@@ -4851,15 +5647,15 @@
       </c>
       <c r="G53" s="9"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:11">
       <c r="G54" s="9"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:11">
       <c r="G55" s="9"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:11">
       <c r="A56" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C56" s="13" t="str">
         <f>+D56</f>
@@ -4877,7 +5673,7 @@
         <v>n.a.</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:11">
       <c r="A57" t="str">
         <f>+A39</f>
         <v>Lag, persistence (AR1)</v>
@@ -4893,7 +5689,7 @@
       </c>
       <c r="G57" s="9"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:11">
       <c r="A58" t="str">
         <f>+A40</f>
         <v>Expectation (t+1)</v>
@@ -4911,13 +5707,13 @@
       </c>
       <c r="G58" s="9"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:11">
       <c r="A59" t="str">
         <f>+A41</f>
         <v>Real Monetary Conditions Index (RMCI)</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E59" s="13" t="s">
         <v>250</v>
@@ -4927,12 +5723,12 @@
       </c>
       <c r="G59" s="9"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:11">
       <c r="A60" t="s">
         <v>20</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E60">
         <v>0.25</v>
@@ -4942,7 +5738,7 @@
       </c>
       <c r="G60" s="9"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:11">
       <c r="A61" t="str">
         <f>+A53</f>
         <v>Weight of RIR in RMCI (or RIR direct effect, if RMCI n.a.)</v>
@@ -4956,12 +5752,12 @@
       </c>
       <c r="G61" s="9"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:11">
       <c r="A62" s="3" t="s">
         <v>280</v>
       </c>
       <c r="B62" s="57" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E62" s="39">
         <v>0.08</v>
@@ -4972,14 +5768,14 @@
       </c>
       <c r="G62" s="9"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:11">
       <c r="A63" s="3"/>
       <c r="F63" s="42"/>
       <c r="G63" s="9"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:11">
       <c r="A64" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C64" s="13" t="str">
         <f>+D64</f>
@@ -4996,12 +5792,12 @@
         <v>n.a.?</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:11">
       <c r="A65" t="s">
         <v>25</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E65" s="39">
         <f>0.37*0.8</f>
@@ -5012,12 +5808,12 @@
       </c>
       <c r="G65" s="9"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:11">
       <c r="A66" t="s">
         <v>26</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E66" s="39">
         <v>0.1</v>
@@ -5028,12 +5824,12 @@
       </c>
       <c r="G66" s="9"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:11">
       <c r="A67" t="s">
         <v>27</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E67" s="39">
         <v>0.03</v>
@@ -5041,12 +5837,12 @@
       <c r="F67" s="42"/>
       <c r="G67" s="9"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:11">
       <c r="A68" t="s">
         <v>28</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E68" s="39">
         <f>(1-0.37-0.1-0.03)</f>
@@ -5055,7 +5851,7 @@
       <c r="F68" s="42"/>
       <c r="G68" s="9"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:11">
       <c r="A69" t="s">
         <v>24</v>
       </c>
@@ -5071,7 +5867,7 @@
       </c>
       <c r="G69" s="9"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:11">
       <c r="A70" t="s">
         <v>0</v>
       </c>
@@ -5080,9 +5876,9 @@
       </c>
       <c r="G70" s="9"/>
     </row>
-    <row r="71" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:11" s="61" customFormat="1">
       <c r="A71" s="58" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B71" s="59" t="s">
         <v>288</v>
@@ -5108,7 +5904,7 @@
         <v>IS eq. used</v>
       </c>
     </row>
-    <row r="72" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:11" s="61" customFormat="1">
       <c r="A72" s="61" t="str">
         <f>+A39</f>
         <v>Lag, persistence (AR1)</v>
@@ -5138,7 +5934,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="73" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:11" s="61" customFormat="1">
       <c r="A73" s="61" t="str">
         <f>+A40</f>
         <v>Expectation (t+1)</v>
@@ -5162,7 +5958,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:11" s="61" customFormat="1">
       <c r="A74" s="61" t="s">
         <v>29</v>
       </c>
@@ -5188,7 +5984,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="75" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:11" s="61" customFormat="1">
       <c r="A75" s="61" t="s">
         <v>12</v>
       </c>
@@ -5207,7 +6003,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="76" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:11" s="61" customFormat="1">
       <c r="A76" s="61" t="s">
         <v>30</v>
       </c>
@@ -5236,7 +6032,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="77" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:11" s="61" customFormat="1">
       <c r="A77" s="61" t="s">
         <v>234</v>
       </c>
@@ -5268,7 +6064,7 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="78" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:11" s="61" customFormat="1">
       <c r="A78" s="69" t="s">
         <v>233</v>
       </c>
@@ -5301,7 +6097,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:11">
       <c r="A79" s="3"/>
       <c r="B79" s="34"/>
       <c r="C79" s="35"/>
@@ -5310,7 +6106,7 @@
       <c r="G79" s="37"/>
       <c r="H79" s="33"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:11">
       <c r="A80" s="1" t="s">
         <v>43</v>
       </c>
@@ -5323,7 +6119,7 @@
       </c>
       <c r="G80" s="9"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:11">
       <c r="A81" t="s">
         <v>34</v>
       </c>
@@ -5339,7 +6135,7 @@
       </c>
       <c r="G81" s="9"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:11">
       <c r="A82" t="s">
         <v>35</v>
       </c>
@@ -5354,7 +6150,7 @@
       </c>
       <c r="G82" s="9"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:11">
       <c r="A83" t="s">
         <v>36</v>
       </c>
@@ -5369,12 +6165,12 @@
       </c>
       <c r="G83" s="9"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:11">
       <c r="A84" t="s">
         <v>37</v>
       </c>
       <c r="B84" s="55" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E84" s="41">
         <v>-0.83350000000000002</v>
@@ -5384,12 +6180,12 @@
       </c>
       <c r="G84" s="9"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:11">
       <c r="A85" t="s">
         <v>38</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E85" s="41">
         <v>0.17780000000000001</v>
@@ -5397,7 +6193,7 @@
       <c r="F85" s="42"/>
       <c r="G85" s="9"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:11">
       <c r="E86" s="41" t="str">
         <f>IF(ABS(E81+E82+E83+E85+E84-1)&gt;0.01,"check","")</f>
         <v/>
@@ -5405,9 +6201,9 @@
       <c r="F86" s="42"/>
       <c r="G86" s="9"/>
     </row>
-    <row r="87" spans="1:11" ht="16.75" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:11" ht="16.75">
       <c r="A87" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F87" s="44" t="str">
         <f>+IF(ABS(F81+F82+F83-F84-1)&gt;0.01,"check","")</f>
@@ -5417,13 +6213,13 @@
         <v>264</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:11">
       <c r="A88" t="str">
         <f>+A39</f>
         <v>Lag, persistence (AR1)</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C88" s="9">
         <v>0.5</v>
@@ -5457,7 +6253,7 @@
         <v>0.66999999999999993</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:11">
       <c r="A89" t="str">
         <f>+A40</f>
         <v>Expectation (t+1)</v>
@@ -5497,7 +6293,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:11">
       <c r="A90" t="s">
         <v>45</v>
       </c>
@@ -5532,7 +6328,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:11">
       <c r="A91" s="39" t="s">
         <v>50</v>
       </c>
@@ -5561,7 +6357,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="92" spans="1:11">
       <c r="A92" t="s">
         <v>237</v>
       </c>
@@ -5598,7 +6394,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="93" spans="1:11">
       <c r="A93" s="3" t="s">
         <v>242</v>
       </c>
@@ -5634,7 +6430,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:11">
       <c r="A94" s="3"/>
       <c r="B94" s="19"/>
       <c r="C94" s="13"/>
@@ -5642,9 +6438,9 @@
       <c r="F94" s="42"/>
       <c r="G94" s="31"/>
     </row>
-    <row r="95" spans="1:11" ht="16.75" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:11" ht="16.75">
       <c r="A95" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F95" s="42"/>
       <c r="G95" s="9"/>
@@ -5656,13 +6452,13 @@
       </c>
       <c r="K95" s="13"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="96" spans="1:11">
       <c r="A96" t="str">
         <f>+A88</f>
         <v>Lag, persistence (AR1)</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C96" s="9">
         <v>0.5</v>
@@ -5687,7 +6483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="97" spans="1:11">
       <c r="A97" t="str">
         <f t="shared" ref="A97:A98" si="1">+A89</f>
         <v>Expectation (t+1)</v>
@@ -5717,7 +6513,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="98" spans="1:11">
       <c r="A98" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">Real marginal cost (RMC) </v>
@@ -5744,12 +6540,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="99" spans="1:11">
       <c r="A99" t="s">
         <v>49</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C99" s="13" t="s">
         <v>250</v>
@@ -5771,12 +6567,12 @@
         <v>n.a.</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:11">
       <c r="A100" t="s">
+        <v>361</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="C100" s="13">
         <f>-1.6*0.3</f>
@@ -5793,7 +6589,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="101" spans="1:11">
       <c r="A101" t="s">
         <v>256</v>
       </c>
@@ -5820,7 +6616,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="102" spans="1:11">
       <c r="A102" s="3" t="s">
         <v>285</v>
       </c>
@@ -5849,7 +6645,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="103" spans="1:11">
       <c r="A103" s="3"/>
       <c r="B103" s="20"/>
       <c r="C103" s="13"/>
@@ -5858,9 +6654,9 @@
       <c r="G103" s="31"/>
       <c r="H103" s="13"/>
     </row>
-    <row r="104" spans="1:11" ht="16.75" x14ac:dyDescent="0.75">
+    <row r="104" spans="1:11" ht="16.75">
       <c r="A104" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F104" s="43" t="s">
         <v>250</v>
@@ -5875,13 +6671,13 @@
         <v>240</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="105" spans="1:11">
       <c r="A105" t="str">
         <f>+A88</f>
         <v>Lag, persistence (AR1)</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C105" s="9">
         <v>0.8</v>
@@ -5893,7 +6689,7 @@
       <c r="G105" s="9"/>
       <c r="H105" s="13"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="106" spans="1:11">
       <c r="A106" t="str">
         <f>+A89</f>
         <v>Expectation (t+1)</v>
@@ -5910,13 +6706,13 @@
       <c r="F106" s="42"/>
       <c r="G106" s="9"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="107" spans="1:11">
       <c r="A107" t="str">
         <f>+A90</f>
         <v xml:space="preserve">Real marginal cost (RMC) </v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C107" s="9">
         <v>0.3</v>
@@ -5927,12 +6723,12 @@
       <c r="F107" s="42"/>
       <c r="G107" s="9"/>
     </row>
-    <row r="108" spans="1:11" ht="17.75" x14ac:dyDescent="0.95">
+    <row r="108" spans="1:11" ht="17.75">
       <c r="A108" t="s">
         <v>53</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C108" s="13" t="s">
         <v>250</v>
@@ -5946,7 +6742,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="109" spans="1:11">
       <c r="A109" s="3" t="s">
         <v>286</v>
       </c>
@@ -5962,7 +6758,7 @@
       <c r="F109" s="42"/>
       <c r="G109" s="9"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:11">
       <c r="A110" s="3"/>
       <c r="B110" s="20"/>
       <c r="C110" s="13"/>
@@ -5970,13 +6766,13 @@
       <c r="F110" s="42"/>
       <c r="G110" s="9"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="111" spans="1:11">
       <c r="A111" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F111" s="42"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="112" spans="1:11">
       <c r="A112" t="s">
         <v>55</v>
       </c>
@@ -6007,7 +6803,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="113" spans="1:11">
       <c r="A113" t="s">
         <v>54</v>
       </c>
@@ -6034,7 +6830,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="114" spans="1:11">
       <c r="A114" t="s">
         <v>56</v>
       </c>
@@ -6060,24 +6856,24 @@
         <v>241</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="115" spans="1:11">
       <c r="F115" s="42"/>
       <c r="G115" s="9"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="116" spans="1:11">
       <c r="A116" s="1" t="s">
         <v>232</v>
       </c>
       <c r="F116" s="42"/>
       <c r="G116" s="9"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="117" spans="1:11">
       <c r="A117" t="str">
         <f>+A39</f>
         <v>Lag, persistence (AR1)</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C117" s="9">
         <v>0.8</v>
@@ -6107,12 +6903,12 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="118" spans="1:11">
       <c r="A118" t="s">
         <v>60</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C118" s="9">
         <v>0.25</v>
@@ -6143,12 +6939,12 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="119" spans="1:11">
       <c r="A119" t="s">
         <v>11</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C119" s="9">
         <v>0.2</v>
@@ -6179,7 +6975,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="120" spans="1:11">
       <c r="A120" t="s">
         <v>281</v>
       </c>
@@ -6214,7 +7010,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="121" spans="1:11">
       <c r="A121" t="s">
         <v>64</v>
       </c>
@@ -6246,7 +7042,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="122" spans="1:11">
       <c r="A122" t="s">
         <v>63</v>
       </c>
@@ -6278,23 +7074,23 @@
         <v>250</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="123" spans="1:11">
       <c r="F123" s="42"/>
       <c r="G123" s="9"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="124" spans="1:11">
       <c r="A124" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F124" s="42"/>
       <c r="G124" s="9"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="125" spans="1:11">
       <c r="A125" t="s">
         <v>66</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C125" s="13" t="s">
         <v>257</v>
@@ -6321,12 +7117,12 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="126" spans="1:11">
       <c r="A126" t="s">
         <v>67</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C126" s="9">
         <v>0.2</v>
@@ -6353,12 +7149,12 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="127" spans="1:11">
       <c r="A127" t="s">
         <v>289</v>
       </c>
       <c r="B127" s="55" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C127" s="9">
         <v>0.8</v>
@@ -6375,7 +7171,7 @@
         <v>0.19999999999999996</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="128" spans="1:11">
       <c r="A128" t="s">
         <v>68</v>
       </c>
@@ -6405,7 +7201,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="129" spans="1:11">
       <c r="A129" t="s">
         <v>70</v>
       </c>
@@ -6432,7 +7228,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="130" spans="1:11">
       <c r="A130" t="s">
         <v>72</v>
       </c>
@@ -6459,12 +7255,12 @@
         <v>250</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="131" spans="1:11">
       <c r="A131" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C131" s="9">
         <v>-0.85</v>
@@ -6486,12 +7282,12 @@
         <v>250</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="132" spans="1:11">
       <c r="F132" s="42"/>
       <c r="G132" s="9"/>
       <c r="H132" s="13"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="133" spans="1:11">
       <c r="A133" s="1" t="s">
         <v>74</v>
       </c>
@@ -6517,7 +7313,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="134" spans="1:11">
       <c r="A134" t="str">
         <f>+A39</f>
         <v>Lag, persistence (AR1)</v>
@@ -6532,12 +7328,12 @@
       <c r="G134" s="9"/>
       <c r="H134" s="13"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="135" spans="1:11">
       <c r="A135" t="s">
         <v>252</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C135" s="12">
         <f>-0.5</f>
@@ -6546,7 +7342,7 @@
       <c r="F135" s="42"/>
       <c r="G135" s="9"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="136" spans="1:11">
       <c r="A136" t="s">
         <v>75</v>
       </c>
@@ -6559,18 +7355,18 @@
       <c r="F136" s="42"/>
       <c r="G136" s="9"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="137" spans="1:11">
       <c r="F137" s="42"/>
       <c r="G137" s="9"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="138" spans="1:11">
       <c r="A138" s="1" t="s">
         <v>223</v>
       </c>
       <c r="F138" s="42"/>
       <c r="G138" s="9"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="139" spans="1:11">
       <c r="A139" t="s">
         <v>51</v>
       </c>
@@ -6583,7 +7379,7 @@
       <c r="F139" s="42"/>
       <c r="G139" s="9"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="140" spans="1:11">
       <c r="A140" t="s">
         <v>78</v>
       </c>
@@ -6596,7 +7392,7 @@
       <c r="F140" s="42"/>
       <c r="G140" s="9"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="141" spans="1:11">
       <c r="A141" t="s">
         <v>258</v>
       </c>
@@ -6620,7 +7416,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="142" spans="1:11">
       <c r="A142" t="s">
         <v>79</v>
       </c>
@@ -6630,7 +7426,7 @@
       <c r="F142" s="42"/>
       <c r="G142" s="9"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="143" spans="1:11">
       <c r="A143" t="s">
         <v>80</v>
       </c>
@@ -6642,7 +7438,7 @@
       </c>
       <c r="G143" s="9"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="144" spans="1:11">
       <c r="A144" t="s">
         <v>81</v>
       </c>
@@ -6654,7 +7450,7 @@
       </c>
       <c r="G144" s="9"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="145" spans="1:11">
       <c r="A145" t="s">
         <v>82</v>
       </c>
@@ -6666,7 +7462,7 @@
       </c>
       <c r="G145" s="9"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="146" spans="1:11">
       <c r="A146" t="s">
         <v>83</v>
       </c>
@@ -6690,7 +7486,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="147" spans="1:11">
       <c r="A147" t="s">
         <v>102</v>
       </c>
@@ -6706,7 +7502,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="148" spans="1:11">
       <c r="A148" t="s">
         <v>101</v>
       </c>
@@ -6719,7 +7515,7 @@
       <c r="F148" s="42"/>
       <c r="G148" s="9"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="149" spans="1:11">
       <c r="A149" t="s">
         <v>244</v>
       </c>
@@ -6740,7 +7536,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="150" spans="1:11">
       <c r="B150" s="53" t="str">
         <f>+B4</f>
         <v>QMFM (this study MINECOFIN)</v>
@@ -6752,14 +7548,14 @@
       <c r="F150" s="42"/>
       <c r="G150" s="9"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="151" spans="1:11">
       <c r="A151" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F151" s="42"/>
       <c r="G151" s="9"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="152" spans="1:11">
       <c r="A152" t="s">
         <v>95</v>
       </c>
@@ -6772,7 +7568,7 @@
       <c r="F152" s="42"/>
       <c r="G152" s="9"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="153" spans="1:11">
       <c r="A153" t="s">
         <v>96</v>
       </c>
@@ -6785,7 +7581,7 @@
       <c r="F153" s="42"/>
       <c r="G153" s="9"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="154" spans="1:11">
       <c r="A154" t="s">
         <v>208</v>
       </c>
@@ -6795,12 +7591,12 @@
       <c r="F154" s="42"/>
       <c r="G154" s="9"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="155" spans="1:11">
       <c r="A155" t="s">
         <v>97</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C155" s="22" t="s">
         <v>253</v>
@@ -6822,12 +7618,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="156" spans="1:11">
       <c r="A156" t="s">
         <v>98</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C156" s="24">
         <v>8.1579999999999995</v>
@@ -6836,12 +7632,12 @@
       <c r="G156" s="9"/>
       <c r="H156" s="15"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="157" spans="1:11">
       <c r="A157" t="s">
         <v>99</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C157" s="13" t="s">
         <v>261</v>
@@ -6863,12 +7659,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="158" spans="1:11">
       <c r="A158" t="s">
         <v>100</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C158" s="9">
         <v>0</v>
@@ -6882,7 +7678,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="159" spans="1:11">
       <c r="A159" t="s">
         <v>103</v>
       </c>
@@ -6898,7 +7694,7 @@
       <c r="G159" s="9"/>
       <c r="H159" s="11"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="160" spans="1:11">
       <c r="A160" t="s">
         <v>104</v>
       </c>
@@ -6927,12 +7723,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="161" spans="1:9">
       <c r="A161" t="s">
         <v>105</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C161" s="9">
         <f>+C166-C209-C160</f>
@@ -6959,7 +7755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="162" spans="1:9">
       <c r="A162" t="s">
         <v>111</v>
       </c>
@@ -6972,32 +7768,32 @@
       <c r="F162" s="42"/>
       <c r="G162" s="9"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="163" spans="1:9">
       <c r="A163" t="s">
         <v>112</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F163" s="42"/>
       <c r="G163" s="9"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="164" spans="1:9">
       <c r="A164" t="s">
         <v>268</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F164" s="42"/>
       <c r="G164" s="9"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="165" spans="1:9">
       <c r="A165" t="s">
         <v>110</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C165" s="9">
         <v>-8</v>
@@ -7005,12 +7801,12 @@
       <c r="F165" s="42"/>
       <c r="G165" s="9"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="166" spans="1:9">
       <c r="A166" t="s">
         <v>300</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C166" s="9">
         <v>2</v>
@@ -7031,7 +7827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="167" spans="1:9">
       <c r="A167" t="s">
         <v>301</v>
       </c>
@@ -7044,18 +7840,18 @@
       <c r="F167" s="42"/>
       <c r="G167" s="9"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="168" spans="1:9">
       <c r="F168" s="42"/>
       <c r="G168" s="9"/>
     </row>
-    <row r="169" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="169" spans="1:9" outlineLevel="1">
       <c r="A169" s="1" t="s">
         <v>297</v>
       </c>
       <c r="F169" s="42"/>
       <c r="G169" s="9"/>
     </row>
-    <row r="170" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="170" spans="1:9" outlineLevel="1">
       <c r="A170" t="s">
         <v>113</v>
       </c>
@@ -7068,7 +7864,7 @@
       <c r="F170" s="42"/>
       <c r="G170" s="9"/>
     </row>
-    <row r="171" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="171" spans="1:9" outlineLevel="1">
       <c r="A171" t="s">
         <v>114</v>
       </c>
@@ -7079,7 +7875,7 @@
       <c r="F171" s="42"/>
       <c r="G171" s="9"/>
     </row>
-    <row r="172" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="172" spans="1:9" outlineLevel="1">
       <c r="A172" t="s">
         <v>115</v>
       </c>
@@ -7090,7 +7886,7 @@
       <c r="F172" s="42"/>
       <c r="G172" s="9"/>
     </row>
-    <row r="173" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="173" spans="1:9" outlineLevel="1">
       <c r="A173" t="s">
         <v>116</v>
       </c>
@@ -7101,7 +7897,7 @@
       <c r="F173" s="42"/>
       <c r="G173" s="9"/>
     </row>
-    <row r="174" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="174" spans="1:9" outlineLevel="1">
       <c r="A174" t="s">
         <v>117</v>
       </c>
@@ -7112,7 +7908,7 @@
       <c r="F174" s="42"/>
       <c r="G174" s="9"/>
     </row>
-    <row r="175" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="175" spans="1:9" outlineLevel="1">
       <c r="A175" t="s">
         <v>118</v>
       </c>
@@ -7123,7 +7919,7 @@
       <c r="F175" s="42"/>
       <c r="G175" s="9"/>
     </row>
-    <row r="176" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="176" spans="1:9" outlineLevel="1">
       <c r="A176" t="s">
         <v>121</v>
       </c>
@@ -7140,7 +7936,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="177" spans="1:8" outlineLevel="1">
       <c r="A177" t="s">
         <v>119</v>
       </c>
@@ -7157,7 +7953,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="178" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="178" spans="1:8" outlineLevel="1">
       <c r="A178" t="s">
         <v>120</v>
       </c>
@@ -7175,7 +7971,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="179" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="179" spans="1:8" outlineLevel="1">
       <c r="A179" t="s">
         <v>122</v>
       </c>
@@ -7192,7 +7988,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="180" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="180" spans="1:8" outlineLevel="1">
       <c r="A180" t="s">
         <v>224</v>
       </c>
@@ -7203,7 +7999,7 @@
       <c r="F180" s="42"/>
       <c r="G180" s="9"/>
     </row>
-    <row r="181" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="181" spans="1:8" outlineLevel="1">
       <c r="A181" t="s">
         <v>123</v>
       </c>
@@ -7217,7 +8013,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="182" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="182" spans="1:8" outlineLevel="1">
       <c r="A182" t="s">
         <v>124</v>
       </c>
@@ -7228,7 +8024,7 @@
       <c r="F182" s="42"/>
       <c r="G182" s="9"/>
     </row>
-    <row r="183" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="183" spans="1:8" outlineLevel="1">
       <c r="A183" t="s">
         <v>125</v>
       </c>
@@ -7239,12 +8035,12 @@
       <c r="F183" s="42"/>
       <c r="G183" s="9"/>
     </row>
-    <row r="184" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="184" spans="1:8" outlineLevel="1">
       <c r="C184" s="26"/>
       <c r="F184" s="42"/>
       <c r="G184" s="9"/>
     </row>
-    <row r="185" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="185" spans="1:8" outlineLevel="1">
       <c r="A185" s="1" t="str">
         <f>+A169</f>
         <v>Standard deviation (σ or SE=σ/√n)</v>
@@ -7253,7 +8049,7 @@
       <c r="F185" s="42"/>
       <c r="G185" s="9"/>
     </row>
-    <row r="186" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="186" spans="1:8" outlineLevel="1">
       <c r="A186" t="s">
         <v>140</v>
       </c>
@@ -7270,7 +8066,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="187" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="187" spans="1:8" outlineLevel="1">
       <c r="A187" t="s">
         <v>142</v>
       </c>
@@ -7281,7 +8077,7 @@
       <c r="F187" s="42"/>
       <c r="G187" s="9"/>
     </row>
-    <row r="188" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="188" spans="1:8" outlineLevel="1">
       <c r="A188" t="s">
         <v>141</v>
       </c>
@@ -7292,7 +8088,7 @@
       <c r="F188" s="42"/>
       <c r="G188" s="9"/>
     </row>
-    <row r="189" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="189" spans="1:8" outlineLevel="1">
       <c r="A189" t="s">
         <v>146</v>
       </c>
@@ -7303,7 +8099,7 @@
       <c r="F189" s="42"/>
       <c r="G189" s="9"/>
     </row>
-    <row r="190" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="190" spans="1:8" outlineLevel="1">
       <c r="A190" t="s">
         <v>225</v>
       </c>
@@ -7314,7 +8110,7 @@
       <c r="F190" s="42"/>
       <c r="G190" s="9"/>
     </row>
-    <row r="191" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="191" spans="1:8" outlineLevel="1">
       <c r="A191" t="s">
         <v>147</v>
       </c>
@@ -7331,7 +8127,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="192" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="192" spans="1:8" outlineLevel="1">
       <c r="A192" t="s">
         <v>148</v>
       </c>
@@ -7342,7 +8138,7 @@
       <c r="F192" s="42"/>
       <c r="G192" s="9"/>
     </row>
-    <row r="193" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="193" spans="1:9" outlineLevel="1">
       <c r="A193" t="s">
         <v>149</v>
       </c>
@@ -7353,7 +8149,7 @@
       <c r="F193" s="42"/>
       <c r="G193" s="9"/>
     </row>
-    <row r="194" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="194" spans="1:9" outlineLevel="1">
       <c r="A194" t="s">
         <v>150</v>
       </c>
@@ -7364,7 +8160,7 @@
       <c r="F194" s="42"/>
       <c r="G194" s="9"/>
     </row>
-    <row r="195" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="195" spans="1:9" outlineLevel="1">
       <c r="A195" t="s">
         <v>151</v>
       </c>
@@ -7375,7 +8171,7 @@
       <c r="F195" s="42"/>
       <c r="G195" s="9"/>
     </row>
-    <row r="196" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="196" spans="1:9" outlineLevel="1">
       <c r="A196" t="s">
         <v>152</v>
       </c>
@@ -7392,7 +8188,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="197" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="197" spans="1:9" outlineLevel="1">
       <c r="A197" t="s">
         <v>153</v>
       </c>
@@ -7406,7 +8202,7 @@
       <c r="F197" s="42"/>
       <c r="G197" s="9"/>
     </row>
-    <row r="198" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="198" spans="1:9" outlineLevel="1">
       <c r="A198" t="s">
         <v>154</v>
       </c>
@@ -7420,7 +8216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="199" spans="1:9" outlineLevel="1">
       <c r="A199" t="s">
         <v>155</v>
       </c>
@@ -7434,7 +8230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="200" spans="1:9" outlineLevel="1">
       <c r="A200" t="s">
         <v>156</v>
       </c>
@@ -7445,7 +8241,7 @@
       <c r="F200" s="42"/>
       <c r="G200" s="9"/>
     </row>
-    <row r="201" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.75">
+    <row r="201" spans="1:9" outlineLevel="1">
       <c r="A201" t="s">
         <v>226</v>
       </c>
@@ -7459,11 +8255,11 @@
       <c r="F201" s="42"/>
       <c r="G201" s="9"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="202" spans="1:9">
       <c r="F202" s="42"/>
       <c r="G202" s="9"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="203" spans="1:9">
       <c r="A203" s="1" t="s">
         <v>191</v>
       </c>
@@ -7478,7 +8274,7 @@
       <c r="F203" s="42"/>
       <c r="G203" s="9"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="204" spans="1:9">
       <c r="A204" s="39" t="s">
         <v>269</v>
       </c>
@@ -7493,7 +8289,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="205" spans="1:9">
       <c r="A205" t="s">
         <v>187</v>
       </c>
@@ -7520,7 +8316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="206" spans="1:9">
       <c r="A206" t="s">
         <v>227</v>
       </c>
@@ -7544,7 +8340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="207" spans="1:9">
       <c r="A207" t="s">
         <v>188</v>
       </c>
@@ -7565,7 +8361,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="208" spans="1:9">
       <c r="A208" t="s">
         <v>190</v>
       </c>
@@ -7595,7 +8391,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="209" spans="1:9">
       <c r="A209" t="s">
         <v>189</v>
       </c>
@@ -7621,14 +8417,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="210" spans="1:9">
       <c r="A210" s="1" t="s">
         <v>192</v>
       </c>
       <c r="F210" s="42"/>
       <c r="G210" s="9"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="211" spans="1:9">
       <c r="A211" t="s">
         <v>259</v>
       </c>
@@ -7651,7 +8447,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="212" spans="1:9">
       <c r="A212" t="s">
         <v>194</v>
       </c>
@@ -7671,7 +8467,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="213" spans="1:9">
       <c r="A213" t="s">
         <v>195</v>
       </c>
@@ -7693,7 +8489,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="214" spans="1:9">
       <c r="A214" t="s">
         <v>260</v>
       </c>
@@ -7712,7 +8508,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="215" spans="1:9">
       <c r="A215" t="s">
         <v>196</v>
       </c>
@@ -7728,7 +8524,7 @@
       <c r="F215" s="42"/>
       <c r="G215" s="9"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="216" spans="1:9">
       <c r="A216" t="s">
         <v>197</v>
       </c>
@@ -7744,7 +8540,7 @@
       <c r="F216" s="42"/>
       <c r="G216" s="9"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="217" spans="1:9">
       <c r="A217" t="s">
         <v>198</v>
       </c>
@@ -7760,7 +8556,7 @@
       <c r="F217" s="42"/>
       <c r="G217" s="9"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="218" spans="1:9">
       <c r="A218" t="s">
         <v>199</v>
       </c>
@@ -7779,19 +8575,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="219" spans="1:9">
       <c r="A219" s="1" t="s">
         <v>193</v>
       </c>
       <c r="F219" s="42"/>
       <c r="G219" s="9"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="220" spans="1:9">
       <c r="A220" t="s">
         <v>200</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D220">
         <v>0.25</v>
@@ -7802,7 +8598,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="221" spans="1:9">
       <c r="A221" t="s">
         <v>201</v>
       </c>
@@ -7818,7 +8614,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="222" spans="1:9">
       <c r="A222" t="s">
         <v>203</v>
       </c>
@@ -7834,7 +8630,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="223" spans="1:9">
       <c r="A223" t="s">
         <v>202</v>
       </c>
@@ -7850,7 +8646,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="224" spans="1:9">
       <c r="A224" t="s">
         <v>204</v>
       </c>
@@ -7863,7 +8659,7 @@
       <c r="F224" s="42"/>
       <c r="G224" s="9"/>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="225" spans="1:7">
       <c r="A225" t="s">
         <v>205</v>
       </c>
@@ -7876,7 +8672,7 @@
       <c r="F225" s="42"/>
       <c r="G225" s="9"/>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="226" spans="1:7">
       <c r="A226" t="s">
         <v>206</v>
       </c>
@@ -7889,7 +8685,7 @@
       <c r="F226" s="42"/>
       <c r="G226" s="9"/>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="227" spans="1:7">
       <c r="A227" t="s">
         <v>207</v>
       </c>
@@ -7902,16 +8698,16 @@
       <c r="F227" s="42"/>
       <c r="G227" s="9"/>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="228" spans="1:7">
       <c r="G228" s="9"/>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="229" spans="1:7">
       <c r="A229" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G229" s="9"/>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="230" spans="1:7">
       <c r="A230" t="s">
         <v>228</v>
       </c>
@@ -7926,7 +8722,7 @@
       </c>
       <c r="G230" s="9"/>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="231" spans="1:7">
       <c r="A231" t="s">
         <v>229</v>
       </c>
@@ -7941,7 +8737,7 @@
       </c>
       <c r="G231" s="9"/>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="232" spans="1:7">
       <c r="A232" t="s">
         <v>209</v>
       </c>
@@ -7956,7 +8752,7 @@
       </c>
       <c r="G232" s="9"/>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="233" spans="1:7">
       <c r="A233" t="s">
         <v>213</v>
       </c>
@@ -7971,7 +8767,7 @@
       </c>
       <c r="G233" s="9"/>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="234" spans="1:7">
       <c r="A234" t="s">
         <v>214</v>
       </c>
@@ -7986,10 +8782,10 @@
       </c>
       <c r="G234" s="9"/>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="235" spans="1:7">
       <c r="G235" s="9"/>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="236" spans="1:7">
       <c r="A236" t="s">
         <v>217</v>
       </c>
@@ -8004,12 +8800,12 @@
       </c>
       <c r="G236" s="9"/>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="237" spans="1:7">
       <c r="A237" t="s">
         <v>219</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C237" s="13" t="s">
         <v>250</v>
@@ -8021,11 +8817,1699 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="The model specfication no longer have this IS curve specification" sqref="A71:A78" xr:uid="{022E53BD-FF77-4D7E-BC82-E63BF26AEE3D}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="The model specfication no longer have this IS curve specification" sqref="A71:A78" xr:uid="{BE084419-23BD-46CD-9467-F318ABD2F8A1}"/>
   </dataValidations>
   <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup scale="70" orientation="landscape" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DA45FF5-F233-4AC2-840A-6D28A8836A24}">
+  <dimension ref="B1:D225"/>
+  <sheetFormatPr defaultRowHeight="14.75" outlineLevelRow="1"/>
+  <cols>
+    <col min="2" max="2" width="52.86328125" customWidth="1"/>
+    <col min="3" max="3" width="37.2265625" style="76" customWidth="1"/>
+    <col min="4" max="4" width="13.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="16.5" thickBot="1">
+      <c r="B1" s="84" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1" s="85" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" spans="2:4" s="7" customFormat="1" ht="15.5" thickTop="1">
+      <c r="B2" s="77"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3" s="78" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" s="87"/>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" s="78" t="s">
+        <v>445</v>
+      </c>
+      <c r="C4" s="87"/>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" s="78" t="s">
+        <v>447</v>
+      </c>
+      <c r="C5" s="87"/>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" s="78" t="s">
+        <v>308</v>
+      </c>
+      <c r="C6" s="87"/>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" s="79" t="s">
+        <v>441</v>
+      </c>
+      <c r="C7" s="87" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" s="80" t="s">
+        <v>303</v>
+      </c>
+      <c r="C8" s="87" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" s="78" t="s">
+        <v>309</v>
+      </c>
+      <c r="C9" s="87"/>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" s="80" t="s">
+        <v>312</v>
+      </c>
+      <c r="C10" s="87" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" s="80" t="s">
+        <v>313</v>
+      </c>
+      <c r="C11" s="87" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" s="80" t="s">
+        <v>314</v>
+      </c>
+      <c r="C12" s="87" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" s="78" t="s">
+        <v>315</v>
+      </c>
+      <c r="C13" s="87"/>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" s="80" t="s">
+        <v>303</v>
+      </c>
+      <c r="C14" s="87" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" s="80" t="s">
+        <v>318</v>
+      </c>
+      <c r="C15" s="87" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" s="80"/>
+      <c r="C16" s="87"/>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="78" t="s">
+        <v>446</v>
+      </c>
+      <c r="C17" s="88"/>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="78" t="s">
+        <v>319</v>
+      </c>
+      <c r="C18" s="88"/>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="80" t="s">
+        <v>303</v>
+      </c>
+      <c r="C19" s="87" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="80" t="s">
+        <v>321</v>
+      </c>
+      <c r="C20" s="87" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="78" t="s">
+        <v>309</v>
+      </c>
+      <c r="C21" s="87"/>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" s="80" t="s">
+        <v>303</v>
+      </c>
+      <c r="C22" s="87" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" s="80" t="s">
+        <v>321</v>
+      </c>
+      <c r="C23" s="87" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" s="78" t="s">
+        <v>353</v>
+      </c>
+      <c r="C24" s="87"/>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25" s="80" t="s">
+        <v>303</v>
+      </c>
+      <c r="C25" s="87" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" s="80" t="s">
+        <v>449</v>
+      </c>
+      <c r="C26" s="87" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" s="80"/>
+      <c r="C27" s="87"/>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28" s="78" t="s">
+        <v>329</v>
+      </c>
+      <c r="C28" s="87"/>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29" s="79" t="s">
+        <v>448</v>
+      </c>
+      <c r="C29" s="87" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30" s="78" t="s">
+        <v>328</v>
+      </c>
+      <c r="C30" s="87"/>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31" s="80" t="s">
+        <v>303</v>
+      </c>
+      <c r="C31" s="87" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32" s="80" t="s">
+        <v>325</v>
+      </c>
+      <c r="C32" s="89" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33" s="80"/>
+      <c r="C33" s="89"/>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34" s="78" t="s">
+        <v>352</v>
+      </c>
+      <c r="C34" s="87"/>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35" s="78" t="s">
+        <v>351</v>
+      </c>
+      <c r="C35" s="87"/>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36" s="80" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="87" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="87" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38" s="80" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="87" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="87" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="87" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3">
+      <c r="B41" s="80" t="s">
+        <v>390</v>
+      </c>
+      <c r="C41" s="87" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3">
+      <c r="B42" s="81" t="s">
+        <v>450</v>
+      </c>
+      <c r="C42" s="87"/>
+    </row>
+    <row r="43" spans="2:3">
+      <c r="B43" s="81"/>
+      <c r="C43" s="87"/>
+    </row>
+    <row r="44" spans="2:3">
+      <c r="B44" s="78" t="s">
+        <v>350</v>
+      </c>
+      <c r="C44" s="87"/>
+    </row>
+    <row r="45" spans="2:3">
+      <c r="B45" s="80" t="str">
+        <f t="shared" ref="B45:B50" si="0">+B36</f>
+        <v>Lag, persistence (AR1)</v>
+      </c>
+      <c r="C45" s="87" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3">
+      <c r="B46" s="80" t="str">
+        <f t="shared" si="0"/>
+        <v>Expectation (t+1)</v>
+      </c>
+      <c r="C46" s="87" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3">
+      <c r="B47" s="80" t="str">
+        <f t="shared" si="0"/>
+        <v>Real Monetary Conditions Index (RMCI)</v>
+      </c>
+      <c r="C47" s="87" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3">
+      <c r="B48" s="80" t="str">
+        <f t="shared" si="0"/>
+        <v>Output gap</v>
+      </c>
+      <c r="C48" s="87" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3">
+      <c r="B49" s="80" t="str">
+        <f t="shared" si="0"/>
+        <v>Fiscal impulse</v>
+      </c>
+      <c r="C49" s="87" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3">
+      <c r="B50" s="80" t="str">
+        <f t="shared" si="0"/>
+        <v>Weight of RIR in RMCI (or RIR direct effect, if RMCI n.a.)</v>
+      </c>
+      <c r="C50" s="87" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3">
+      <c r="B51" s="80"/>
+      <c r="C51" s="87"/>
+    </row>
+    <row r="52" spans="2:3">
+      <c r="B52" s="80"/>
+      <c r="C52" s="87"/>
+    </row>
+    <row r="53" spans="2:3">
+      <c r="B53" s="78" t="s">
+        <v>349</v>
+      </c>
+      <c r="C53" s="87"/>
+    </row>
+    <row r="54" spans="2:3">
+      <c r="B54" s="80" t="str">
+        <f>+B36</f>
+        <v>Lag, persistence (AR1)</v>
+      </c>
+      <c r="C54" s="87" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3">
+      <c r="B55" s="80" t="str">
+        <f>+B37</f>
+        <v>Expectation (t+1)</v>
+      </c>
+      <c r="C55" s="87" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3">
+      <c r="B56" s="80" t="str">
+        <f>+B38</f>
+        <v>Real Monetary Conditions Index (RMCI)</v>
+      </c>
+      <c r="C56" s="87" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3">
+      <c r="B57" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="87" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3">
+      <c r="B58" s="80" t="str">
+        <f>+B50</f>
+        <v>Weight of RIR in RMCI (or RIR direct effect, if RMCI n.a.)</v>
+      </c>
+      <c r="C58" s="87" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3">
+      <c r="B59" s="81" t="s">
+        <v>280</v>
+      </c>
+      <c r="C59" s="88" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3">
+      <c r="B60" s="81"/>
+      <c r="C60" s="87"/>
+    </row>
+    <row r="61" spans="2:3">
+      <c r="B61" s="78" t="s">
+        <v>348</v>
+      </c>
+      <c r="C61" s="87"/>
+    </row>
+    <row r="62" spans="2:3">
+      <c r="B62" s="80" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="87" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3">
+      <c r="B63" s="80" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" s="87" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3">
+      <c r="B64" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" s="87" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3">
+      <c r="B65" s="80" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" s="87" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3">
+      <c r="B66" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="87" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3">
+      <c r="B67" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="C67" s="87" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3">
+      <c r="B68" s="78" t="s">
+        <v>412</v>
+      </c>
+      <c r="C68" s="87"/>
+    </row>
+    <row r="69" spans="2:3">
+      <c r="B69" s="80" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69" s="87" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3">
+      <c r="B70" s="80" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70" s="87" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3">
+      <c r="B71" s="80" t="s">
+        <v>36</v>
+      </c>
+      <c r="C71" s="87" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3">
+      <c r="B72" s="80" t="s">
+        <v>37</v>
+      </c>
+      <c r="C72" s="87" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3">
+      <c r="B73" s="80" t="s">
+        <v>38</v>
+      </c>
+      <c r="C73" s="87" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3">
+      <c r="B74" s="80"/>
+      <c r="C74" s="87"/>
+    </row>
+    <row r="75" spans="2:3" ht="16.5">
+      <c r="B75" s="78" t="s">
+        <v>413</v>
+      </c>
+      <c r="C75" s="87"/>
+    </row>
+    <row r="76" spans="2:3">
+      <c r="B76" s="80" t="str">
+        <f>+B36</f>
+        <v>Lag, persistence (AR1)</v>
+      </c>
+      <c r="C76" s="87" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3">
+      <c r="B77" s="80" t="str">
+        <f>+B37</f>
+        <v>Expectation (t+1)</v>
+      </c>
+      <c r="C77" s="87" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3">
+      <c r="B78" s="80" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="87" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3">
+      <c r="B79" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="C79" s="87" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3">
+      <c r="B80" s="80" t="s">
+        <v>237</v>
+      </c>
+      <c r="C80" s="87" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3">
+      <c r="B81" s="81" t="s">
+        <v>242</v>
+      </c>
+      <c r="C81" s="88" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3">
+      <c r="B82" s="81"/>
+      <c r="C82" s="88"/>
+    </row>
+    <row r="83" spans="2:3" ht="16.5">
+      <c r="B83" s="78" t="s">
+        <v>414</v>
+      </c>
+      <c r="C83" s="87"/>
+    </row>
+    <row r="84" spans="2:3">
+      <c r="B84" s="80" t="str">
+        <f>+B76</f>
+        <v>Lag, persistence (AR1)</v>
+      </c>
+      <c r="C84" s="87" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3">
+      <c r="B85" s="80" t="str">
+        <f t="shared" ref="B85:B86" si="1">+B77</f>
+        <v>Expectation (t+1)</v>
+      </c>
+      <c r="C85" s="87" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3">
+      <c r="B86" s="80" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Real marginal cost (RMC) </v>
+      </c>
+      <c r="C86" s="87" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3">
+      <c r="B87" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="C87" s="87" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3">
+      <c r="B88" s="80" t="s">
+        <v>415</v>
+      </c>
+      <c r="C88" s="87" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3">
+      <c r="B89" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C89" s="90" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3">
+      <c r="B90" s="81" t="s">
+        <v>285</v>
+      </c>
+      <c r="C90" s="90" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3">
+      <c r="B91" s="81"/>
+      <c r="C91" s="90"/>
+    </row>
+    <row r="92" spans="2:3" ht="16.5">
+      <c r="B92" s="78" t="s">
+        <v>416</v>
+      </c>
+      <c r="C92" s="87"/>
+    </row>
+    <row r="93" spans="2:3">
+      <c r="B93" s="80" t="str">
+        <f>+B76</f>
+        <v>Lag, persistence (AR1)</v>
+      </c>
+      <c r="C93" s="87" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3">
+      <c r="B94" s="80" t="str">
+        <f>+B77</f>
+        <v>Expectation (t+1)</v>
+      </c>
+      <c r="C94" s="87" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3">
+      <c r="B95" s="80" t="str">
+        <f>+B78</f>
+        <v xml:space="preserve">Real marginal cost (RMC) </v>
+      </c>
+      <c r="C95" s="87" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3">
+      <c r="B96" s="80" t="s">
+        <v>53</v>
+      </c>
+      <c r="C96" s="87" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3">
+      <c r="B97" s="81" t="s">
+        <v>286</v>
+      </c>
+      <c r="C97" s="90" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3">
+      <c r="B98" s="81"/>
+      <c r="C98" s="90"/>
+    </row>
+    <row r="99" spans="2:3">
+      <c r="B99" s="78" t="s">
+        <v>359</v>
+      </c>
+      <c r="C99" s="87"/>
+    </row>
+    <row r="100" spans="2:3">
+      <c r="B100" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C100" s="87" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3">
+      <c r="B101" s="80" t="s">
+        <v>54</v>
+      </c>
+      <c r="C101" s="87" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3">
+      <c r="B102" s="80" t="s">
+        <v>56</v>
+      </c>
+      <c r="C102" s="87" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3">
+      <c r="B103" s="80"/>
+      <c r="C103" s="87"/>
+    </row>
+    <row r="104" spans="2:3">
+      <c r="B104" s="78" t="s">
+        <v>232</v>
+      </c>
+      <c r="C104" s="87"/>
+    </row>
+    <row r="105" spans="2:3">
+      <c r="B105" s="80" t="str">
+        <f>+B36</f>
+        <v>Lag, persistence (AR1)</v>
+      </c>
+      <c r="C105" s="87" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3">
+      <c r="B106" s="80" t="s">
+        <v>60</v>
+      </c>
+      <c r="C106" s="87" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3">
+      <c r="B107" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" s="87" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3">
+      <c r="B108" s="80" t="s">
+        <v>417</v>
+      </c>
+      <c r="C108" s="87" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3">
+      <c r="B109" s="80" t="s">
+        <v>64</v>
+      </c>
+      <c r="C109" s="87" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3">
+      <c r="B110" s="80" t="s">
+        <v>63</v>
+      </c>
+      <c r="C110" s="87" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3">
+      <c r="B111" s="80"/>
+      <c r="C111" s="87"/>
+    </row>
+    <row r="112" spans="2:3">
+      <c r="B112" s="78" t="s">
+        <v>44</v>
+      </c>
+      <c r="C112" s="87"/>
+    </row>
+    <row r="113" spans="2:3">
+      <c r="B113" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="C113" s="87" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3">
+      <c r="B114" s="80" t="s">
+        <v>67</v>
+      </c>
+      <c r="C114" s="87" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3">
+      <c r="B115" s="80" t="s">
+        <v>289</v>
+      </c>
+      <c r="C115" s="87" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3">
+      <c r="B116" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="C116" s="87" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3">
+      <c r="B117" s="80" t="s">
+        <v>70</v>
+      </c>
+      <c r="C117" s="87" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3">
+      <c r="B118" s="80" t="s">
+        <v>72</v>
+      </c>
+      <c r="C118" s="87" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3">
+      <c r="B119" s="80" t="s">
+        <v>375</v>
+      </c>
+      <c r="C119" s="87" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3">
+      <c r="B120" s="80"/>
+      <c r="C120" s="87"/>
+    </row>
+    <row r="121" spans="2:3">
+      <c r="B121" s="78" t="s">
+        <v>74</v>
+      </c>
+      <c r="C121" s="87"/>
+    </row>
+    <row r="122" spans="2:3">
+      <c r="B122" s="80" t="str">
+        <f>+B36</f>
+        <v>Lag, persistence (AR1)</v>
+      </c>
+      <c r="C122" s="87" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3">
+      <c r="B123" s="80" t="s">
+        <v>252</v>
+      </c>
+      <c r="C123" s="87" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3">
+      <c r="B124" s="80" t="s">
+        <v>75</v>
+      </c>
+      <c r="C124" s="87" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3">
+      <c r="B125" s="80"/>
+      <c r="C125" s="87"/>
+    </row>
+    <row r="126" spans="2:3">
+      <c r="B126" s="78" t="s">
+        <v>223</v>
+      </c>
+      <c r="C126" s="87"/>
+    </row>
+    <row r="127" spans="2:3">
+      <c r="B127" s="80" t="s">
+        <v>51</v>
+      </c>
+      <c r="C127" s="87" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3">
+      <c r="B128" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="C128" s="87" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3">
+      <c r="B129" s="80" t="s">
+        <v>418</v>
+      </c>
+      <c r="C129" s="87" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3">
+      <c r="B130" s="80" t="s">
+        <v>79</v>
+      </c>
+      <c r="C130" s="87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="131" spans="2:3">
+      <c r="B131" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="C131" s="87" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3">
+      <c r="B132" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="C132" s="87" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3">
+      <c r="B133" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="C133" s="87" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3">
+      <c r="B134" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="C134" s="87" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3">
+      <c r="B135" s="80" t="s">
+        <v>419</v>
+      </c>
+      <c r="C135" s="87" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3">
+      <c r="B136" s="80" t="s">
+        <v>420</v>
+      </c>
+      <c r="C136" s="87" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="137" spans="2:3">
+      <c r="B137" s="80" t="s">
+        <v>432</v>
+      </c>
+      <c r="C137" s="87" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="138" spans="2:3">
+      <c r="B138" s="80"/>
+      <c r="C138" s="91"/>
+    </row>
+    <row r="139" spans="2:3">
+      <c r="B139" s="78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" s="87"/>
+    </row>
+    <row r="140" spans="2:3">
+      <c r="B140" s="80" t="s">
+        <v>95</v>
+      </c>
+      <c r="C140" s="87" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3">
+      <c r="B141" s="80" t="s">
+        <v>96</v>
+      </c>
+      <c r="C141" s="87" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="142" spans="2:3">
+      <c r="B142" s="80" t="s">
+        <v>208</v>
+      </c>
+      <c r="C142" s="87" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3">
+      <c r="B143" s="80" t="s">
+        <v>97</v>
+      </c>
+      <c r="C143" s="87" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="144" spans="2:3">
+      <c r="B144" s="80" t="s">
+        <v>98</v>
+      </c>
+      <c r="C144" s="87" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="145" spans="2:3">
+      <c r="B145" s="80" t="s">
+        <v>99</v>
+      </c>
+      <c r="C145" s="87" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="146" spans="2:3">
+      <c r="B146" s="80" t="s">
+        <v>421</v>
+      </c>
+      <c r="C146" s="87" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="147" spans="2:3">
+      <c r="B147" s="80" t="s">
+        <v>422</v>
+      </c>
+      <c r="C147" s="87" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="148" spans="2:3">
+      <c r="B148" s="80" t="s">
+        <v>104</v>
+      </c>
+      <c r="C148" s="87" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="149" spans="2:3">
+      <c r="B149" s="80" t="s">
+        <v>105</v>
+      </c>
+      <c r="C149" s="87" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="150" spans="2:3">
+      <c r="B150" s="80" t="s">
+        <v>423</v>
+      </c>
+      <c r="C150" s="87" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="151" spans="2:3">
+      <c r="B151" s="80" t="s">
+        <v>424</v>
+      </c>
+      <c r="C151" s="87" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="152" spans="2:3">
+      <c r="B152" s="80" t="s">
+        <v>425</v>
+      </c>
+      <c r="C152" s="87" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="153" spans="2:3">
+      <c r="B153" s="80" t="s">
+        <v>110</v>
+      </c>
+      <c r="C153" s="87" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="154" spans="2:3">
+      <c r="B154" s="80" t="s">
+        <v>427</v>
+      </c>
+      <c r="C154" s="87" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="155" spans="2:3">
+      <c r="B155" s="80" t="s">
+        <v>301</v>
+      </c>
+      <c r="C155" s="87" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="156" spans="2:3">
+      <c r="B156" s="80"/>
+      <c r="C156" s="87"/>
+    </row>
+    <row r="157" spans="2:3" outlineLevel="1">
+      <c r="B157" s="78" t="s">
+        <v>428</v>
+      </c>
+      <c r="C157" s="87"/>
+    </row>
+    <row r="158" spans="2:3" outlineLevel="1">
+      <c r="B158" s="80" t="s">
+        <v>113</v>
+      </c>
+      <c r="C158" s="87" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="159" spans="2:3" outlineLevel="1">
+      <c r="B159" s="80" t="s">
+        <v>114</v>
+      </c>
+      <c r="C159" s="87" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="160" spans="2:3" outlineLevel="1">
+      <c r="B160" s="80" t="s">
+        <v>115</v>
+      </c>
+      <c r="C160" s="87" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3" outlineLevel="1">
+      <c r="B161" s="80" t="s">
+        <v>116</v>
+      </c>
+      <c r="C161" s="87" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="162" spans="2:3" outlineLevel="1">
+      <c r="B162" s="80" t="s">
+        <v>117</v>
+      </c>
+      <c r="C162" s="87" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="163" spans="2:3" outlineLevel="1">
+      <c r="B163" s="80" t="s">
+        <v>118</v>
+      </c>
+      <c r="C163" s="87" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="164" spans="2:3" outlineLevel="1">
+      <c r="B164" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="C164" s="87" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="165" spans="2:3" outlineLevel="1">
+      <c r="B165" s="80" t="s">
+        <v>119</v>
+      </c>
+      <c r="C165" s="87" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="166" spans="2:3" outlineLevel="1">
+      <c r="B166" s="80" t="s">
+        <v>120</v>
+      </c>
+      <c r="C166" s="87" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="167" spans="2:3" outlineLevel="1">
+      <c r="B167" s="80" t="s">
+        <v>122</v>
+      </c>
+      <c r="C167" s="87" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="168" spans="2:3" outlineLevel="1">
+      <c r="B168" s="80" t="s">
+        <v>224</v>
+      </c>
+      <c r="C168" s="87" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="169" spans="2:3" outlineLevel="1">
+      <c r="B169" s="80" t="s">
+        <v>123</v>
+      </c>
+      <c r="C169" s="87" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="170" spans="2:3" outlineLevel="1">
+      <c r="B170" s="80" t="s">
+        <v>124</v>
+      </c>
+      <c r="C170" s="87" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="171" spans="2:3" outlineLevel="1">
+      <c r="B171" s="80" t="s">
+        <v>125</v>
+      </c>
+      <c r="C171" s="87" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="172" spans="2:3" outlineLevel="1">
+      <c r="B172" s="80"/>
+      <c r="C172" s="87"/>
+    </row>
+    <row r="173" spans="2:3" outlineLevel="1">
+      <c r="B173" s="78" t="str">
+        <f>+B157</f>
+        <v>Standard deviation (σ or SE=σ/√n)</v>
+      </c>
+      <c r="C173" s="87"/>
+    </row>
+    <row r="174" spans="2:3" outlineLevel="1">
+      <c r="B174" s="80" t="s">
+        <v>140</v>
+      </c>
+      <c r="C174" s="87" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="175" spans="2:3" outlineLevel="1">
+      <c r="B175" s="80" t="s">
+        <v>142</v>
+      </c>
+      <c r="C175" s="87" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="176" spans="2:3" outlineLevel="1">
+      <c r="B176" s="80" t="s">
+        <v>141</v>
+      </c>
+      <c r="C176" s="87" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="177" spans="2:3" outlineLevel="1">
+      <c r="B177" s="80" t="s">
+        <v>146</v>
+      </c>
+      <c r="C177" s="87" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="178" spans="2:3" outlineLevel="1">
+      <c r="B178" s="80" t="s">
+        <v>225</v>
+      </c>
+      <c r="C178" s="87" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="179" spans="2:3" outlineLevel="1">
+      <c r="B179" s="80" t="s">
+        <v>147</v>
+      </c>
+      <c r="C179" s="87" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="180" spans="2:3" outlineLevel="1">
+      <c r="B180" s="80" t="s">
+        <v>148</v>
+      </c>
+      <c r="C180" s="87" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="181" spans="2:3" outlineLevel="1">
+      <c r="B181" s="80" t="s">
+        <v>149</v>
+      </c>
+      <c r="C181" s="87" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="182" spans="2:3" outlineLevel="1">
+      <c r="B182" s="80" t="s">
+        <v>150</v>
+      </c>
+      <c r="C182" s="87" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="183" spans="2:3" outlineLevel="1">
+      <c r="B183" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="C183" s="87" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="184" spans="2:3" outlineLevel="1">
+      <c r="B184" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="C184" s="87" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3" outlineLevel="1">
+      <c r="B185" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="C185" s="87" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="186" spans="2:3" outlineLevel="1">
+      <c r="B186" s="80" t="s">
+        <v>154</v>
+      </c>
+      <c r="C186" s="87" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3" outlineLevel="1">
+      <c r="B187" s="80" t="s">
+        <v>155</v>
+      </c>
+      <c r="C187" s="87" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="188" spans="2:3" outlineLevel="1">
+      <c r="B188" s="80" t="s">
+        <v>156</v>
+      </c>
+      <c r="C188" s="87" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="189" spans="2:3" outlineLevel="1">
+      <c r="B189" s="80" t="s">
+        <v>226</v>
+      </c>
+      <c r="C189" s="87" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="190" spans="2:3">
+      <c r="B190" s="80"/>
+      <c r="C190" s="87"/>
+    </row>
+    <row r="191" spans="2:3">
+      <c r="B191" s="78" t="s">
+        <v>191</v>
+      </c>
+      <c r="C191" s="91" t="str">
+        <f>+C1</f>
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="192" spans="2:3">
+      <c r="B192" s="80" t="s">
+        <v>269</v>
+      </c>
+      <c r="C192" s="87" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="193" spans="2:3">
+      <c r="B193" s="80" t="s">
+        <v>187</v>
+      </c>
+      <c r="C193" s="87" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="194" spans="2:3">
+      <c r="B194" s="80" t="s">
+        <v>227</v>
+      </c>
+      <c r="C194" s="87" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="195" spans="2:3">
+      <c r="B195" s="80" t="s">
+        <v>188</v>
+      </c>
+      <c r="C195" s="87" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="196" spans="2:3">
+      <c r="B196" s="80" t="s">
+        <v>190</v>
+      </c>
+      <c r="C196" s="87" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="197" spans="2:3">
+      <c r="B197" s="80" t="s">
+        <v>189</v>
+      </c>
+      <c r="C197" s="87" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="198" spans="2:3">
+      <c r="B198" s="78" t="s">
+        <v>192</v>
+      </c>
+      <c r="C198" s="87"/>
+    </row>
+    <row r="199" spans="2:3">
+      <c r="B199" s="80" t="s">
+        <v>429</v>
+      </c>
+      <c r="C199" s="87" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="200" spans="2:3">
+      <c r="B200" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="C200" s="87" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="201" spans="2:3">
+      <c r="B201" s="80" t="s">
+        <v>195</v>
+      </c>
+      <c r="C201" s="87" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="202" spans="2:3">
+      <c r="B202" s="80" t="s">
+        <v>260</v>
+      </c>
+      <c r="C202" s="87" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="203" spans="2:3">
+      <c r="B203" s="80" t="s">
+        <v>196</v>
+      </c>
+      <c r="C203" s="87" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="204" spans="2:3">
+      <c r="B204" s="80" t="s">
+        <v>197</v>
+      </c>
+      <c r="C204" s="87" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="205" spans="2:3">
+      <c r="B205" s="80" t="s">
+        <v>198</v>
+      </c>
+      <c r="C205" s="87" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="206" spans="2:3">
+      <c r="B206" s="80" t="s">
+        <v>199</v>
+      </c>
+      <c r="C206" s="87" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="207" spans="2:3">
+      <c r="B207" s="78" t="s">
+        <v>193</v>
+      </c>
+      <c r="C207" s="87"/>
+    </row>
+    <row r="208" spans="2:3">
+      <c r="B208" s="80" t="s">
+        <v>200</v>
+      </c>
+      <c r="C208" s="87" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="209" spans="2:3">
+      <c r="B209" s="80" t="s">
+        <v>201</v>
+      </c>
+      <c r="C209" s="87" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="210" spans="2:3">
+      <c r="B210" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="C210" s="87" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="211" spans="2:3">
+      <c r="B211" s="80" t="s">
+        <v>202</v>
+      </c>
+      <c r="C211" s="87" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="212" spans="2:3">
+      <c r="B212" s="80" t="s">
+        <v>204</v>
+      </c>
+      <c r="C212" s="87" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="213" spans="2:3">
+      <c r="B213" s="80" t="s">
+        <v>205</v>
+      </c>
+      <c r="C213" s="87" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="214" spans="2:3">
+      <c r="B214" s="80" t="s">
+        <v>206</v>
+      </c>
+      <c r="C214" s="87" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="215" spans="2:3">
+      <c r="B215" s="80" t="s">
+        <v>207</v>
+      </c>
+      <c r="C215" s="87" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="216" spans="2:3">
+      <c r="B216" s="80"/>
+      <c r="C216" s="87"/>
+    </row>
+    <row r="217" spans="2:3">
+      <c r="B217" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="C217" s="87"/>
+    </row>
+    <row r="218" spans="2:3">
+      <c r="B218" s="82" t="s">
+        <v>228</v>
+      </c>
+      <c r="C218" s="92" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="219" spans="2:3">
+      <c r="B219" s="82" t="s">
+        <v>229</v>
+      </c>
+      <c r="C219" s="92" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="220" spans="2:3">
+      <c r="B220" s="82" t="s">
+        <v>209</v>
+      </c>
+      <c r="C220" s="92" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="221" spans="2:3">
+      <c r="B221" s="82" t="s">
+        <v>213</v>
+      </c>
+      <c r="C221" s="92" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="222" spans="2:3">
+      <c r="B222" s="82" t="s">
+        <v>214</v>
+      </c>
+      <c r="C222" s="92" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="223" spans="2:3">
+      <c r="B223" s="82"/>
+      <c r="C223" s="92"/>
+    </row>
+    <row r="224" spans="2:3">
+      <c r="B224" s="82" t="s">
+        <v>217</v>
+      </c>
+      <c r="C224" s="87" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="225" spans="2:3" ht="15.5" thickBot="1">
+      <c r="B225" s="83" t="s">
+        <v>219</v>
+      </c>
+      <c r="C225" s="93" t="s">
+        <v>433</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
+  <pageSetup scale="70" orientation="landscape" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
 </file>